--- a/docs/pet-expansion/pet-design.xlsx
+++ b/docs/pet-expansion/pet-design.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R3dc5ebd7a9914596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="2" r:id="Rece26d425b6d4f8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pets" sheetId="3" r:id="Ra38bb4a5f57842d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="4" r:id="Rae95bb068d81468d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gear" sheetId="5" r:id="R309e56bc57d94b7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Degrees" sheetId="6" r:id="R7631410d6b184748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Affixes" sheetId="7" r:id="R58f52d0dfd934d62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procs" sheetId="8" r:id="R0bb985e9937c4130"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill families" sheetId="9" r:id="R2ccfa947f7d548ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combat roles" sheetId="10" r:id="R79512fa248574aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" r:id="R6c09fb81bbca4366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="2" r:id="Rd5856b10275c4124"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pets" sheetId="3" r:id="R76b6fe5bdc214f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="4" r:id="Rccf85831b4e7403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gear" sheetId="5" r:id="Ra96389407d90474a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Degrees" sheetId="6" r:id="R6541a9f521ad44e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Affixes" sheetId="7" r:id="R1885c23d15634c41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procs" sheetId="8" r:id="Re956105ed19848c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill families" sheetId="9" r:id="R86740c2c99ac47de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combat roles" sheetId="10" r:id="R53027d0a67e24e33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1673,9 +1673,6 @@
     <x:t xml:space="preserve">Slots: Collar (offense blues), Harness (defense blues), Charm (utility, skill and proc blues). Item names follow D2: [Prefix] Base [of Suffix], e.g. 'Savage Iron Collar of Storms'.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Rarity: Normal (white, 0 blues), Magic (blue, 1-2), Rare (yellow, 3-5). Odds by degree on Degrees; rare names use two random words (D2 rare naming).</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Degrees</x:t>
   </x:si>
   <x:si>
@@ -1722,9 +1719,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Affix tiers available</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tier rule (D2 alvl): an affix tier can roll when its Min degree &lt;= the item's degree; Affixes &gt; Weight picks among the eligible tiers, so higher degrees reach better tiers and, via rare odds, more blues.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Pet level to wear: Min pet level = degree's Monster level from (column B), so pets and owners progress together.</x:t>
@@ -2850,11 +2844,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="164" formatCode="General"/>
     <x:numFmt numFmtId="165" formatCode="0%"/>
     <x:numFmt numFmtId="166" formatCode="0.00%"/>
     <x:numFmt numFmtId="167" formatCode="0.00"/>
+    <x:numFmt numFmtId="200" formatCode="0.0%"/>
   </x:numFmts>
   <x:fonts count="16">
     <x:font>
@@ -3034,7 +3029,7 @@
     <x:xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="34">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -3152,6 +3147,12 @@
     </x:xf>
     <x:xf numFmtId="164" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="6">
@@ -3985,7 +3986,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B19" s="8" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C19" s="10" t="s">
         <x:v>66</x:v>
@@ -9107,7 +9108,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88f12536a57e4fb5"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65735ee03e694529"/>
 </x:worksheet>
 </file>
 
@@ -9256,7 +9257,7 @@
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:f aca="0">Degrees!B6</x:f>
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I6" s="15" t="s">
         <x:v>457</x:v>
@@ -9304,7 +9305,7 @@
       </x:c>
       <x:c r="H7" s="10" t="n">
         <x:f aca="0">Degrees!B7</x:f>
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I7" s="15" t="s">
         <x:v>463</x:v>
@@ -9352,7 +9353,7 @@
       </x:c>
       <x:c r="H8" s="10" t="n">
         <x:f aca="0">Degrees!B8</x:f>
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I8" s="15" t="s">
         <x:v>469</x:v>
@@ -9400,7 +9401,7 @@
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:f aca="0">Degrees!B9</x:f>
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I9" s="15" t="s">
         <x:v>475</x:v>
@@ -9448,7 +9449,7 @@
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:f aca="0">Degrees!B10</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I10" s="15" t="s">
         <x:v>481</x:v>
@@ -9496,7 +9497,7 @@
       </x:c>
       <x:c r="H11" s="10" t="n">
         <x:f aca="0">Degrees!B11</x:f>
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I11" s="15" t="s">
         <x:v>487</x:v>
@@ -9544,7 +9545,7 @@
       </x:c>
       <x:c r="H12" s="10" t="n">
         <x:f aca="0">Degrees!B12</x:f>
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I12" s="15" t="s">
         <x:v>493</x:v>
@@ -9592,7 +9593,7 @@
       </x:c>
       <x:c r="H13" s="10" t="n">
         <x:f aca="0">Degrees!B13</x:f>
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I13" s="15" t="s">
         <x:v>499</x:v>
@@ -9619,13 +9620,13 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="13" t="s">
-        <x:v>503</x:v>
+      <x:c r="A16" s="13" t="str">
+        <x:v>Normal: 0 blues. Magic: 1–2, capped by degree. Rare: 3–6, capped by degree. See Degrees for caps, odds and roll floors. Existing items are not rerolled.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2de37afaa92d4f22"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a091fb883854d92"/>
 </x:worksheet>
 </file>
 
@@ -9641,16 +9642,19 @@
     <x:col min="11" max="13" width="10" style="1" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="11" style="1" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="10" style="1" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="17.25" hidden="0" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>504</x:v>
+        <x:v>503</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>505</x:v>
+        <x:v>504</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
@@ -9658,46 +9662,55 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="s">
         <x:v>506</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="s">
+      <x:c r="D4" s="7" t="s">
         <x:v>507</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="s">
+      <x:c r="E4" s="7" t="s">
         <x:v>508</x:v>
       </x:c>
-      <x:c r="E4" s="7" t="s">
+      <x:c r="F4" s="7" t="s">
         <x:v>509</x:v>
       </x:c>
-      <x:c r="F4" s="7" t="s">
+      <x:c r="G4" s="7" t="s">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="G4" s="7" t="s">
+      <x:c r="H4" s="7" t="s">
         <x:v>511</x:v>
       </x:c>
-      <x:c r="H4" s="7" t="s">
+      <x:c r="I4" s="7" t="s">
         <x:v>512</x:v>
       </x:c>
-      <x:c r="I4" s="7" t="s">
+      <x:c r="J4" s="7" t="s">
         <x:v>513</x:v>
       </x:c>
-      <x:c r="J4" s="7" t="s">
+      <x:c r="K4" s="7" t="s">
         <x:v>514</x:v>
       </x:c>
-      <x:c r="K4" s="7" t="s">
+      <x:c r="L4" s="7" t="s">
         <x:v>515</x:v>
       </x:c>
-      <x:c r="L4" s="7" t="s">
+      <x:c r="M4" s="7" t="s">
         <x:v>516</x:v>
       </x:c>
-      <x:c r="M4" s="7" t="s">
+      <x:c r="N4" s="7" t="s">
         <x:v>517</x:v>
       </x:c>
-      <x:c r="N4" s="7" t="s">
+      <x:c r="O4" s="7" t="s">
         <x:v>518</x:v>
       </x:c>
-      <x:c r="O4" s="7" t="s">
-        <x:v>519</x:v>
+      <x:c r="P4" s="32" t="str">
+        <x:v>Rare: 6 blues weight</x:v>
+      </x:c>
+      <x:c r="Q4" s="32" t="str">
+        <x:v>Max blues</x:v>
+      </x:c>
+      <x:c r="R4" s="32" t="str">
+        <x:v>Minimum roll percentile</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -9708,7 +9721,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="17" t="n">
         <x:v>0.001</x:v>
@@ -9745,23 +9758,32 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="N5" s="19" t="n">
-        <x:f aca="0">H5*(1+Rules!$B$20)+I5*(3*K5+4*L5+MIN(5,Rules!$B$19)*M5)/(K5+L5+M5)</x:f>
-        <x:v>0.5151</x:v>
+        <x:f aca="0">H5*(1+Rules!$B$20*IF(Q5&gt;1,1,0))+I5*(MIN(3,Q5)*K5+MIN(4,Q5)*L5+MIN(5,Q5)*M5+MIN(6,Q5)*P5)/(K5+L5+M5+P5)</x:f>
+        <x:v>0.32999999999999996</x:v>
       </x:c>
       <x:c r="O5" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A5)</x:f>
         <x:v>14</x:v>
       </x:c>
+      <x:c r="P5" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q5" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R5" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="10" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="8" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="8" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="17" t="n">
         <x:v>0.001</x:v>
@@ -9798,23 +9820,32 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N6" s="19" t="n">
-        <x:f aca="0">H6*(1+Rules!$B$20)+I6*(3*K6+4*L6+MIN(5,Rules!$B$19)*M6)/(K6+L6+M6)</x:f>
-        <x:v>0.5776</x:v>
+        <x:f aca="0">H6*(1+Rules!$B$20*IF(Q6&gt;1,1,0))+I6*(MIN(3,Q6)*K6+MIN(4,Q6)*L6+MIN(5,Q6)*M6+MIN(6,Q6)*P6)/(K6+L6+M6+P6)</x:f>
+        <x:v>0.5279999999999999</x:v>
       </x:c>
       <x:c r="O6" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A6)</x:f>
         <x:v>18</x:v>
       </x:c>
+      <x:c r="P6" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R6" s="33" t="n">
+        <x:v>0.0625</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="10" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="8" t="n">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="8" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D7" s="17" t="n">
         <x:v>0.0011</x:v>
@@ -9851,23 +9882,32 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N7" s="19" t="n">
-        <x:f aca="0">H7*(1+Rules!$B$20)+I7*(3*K7+4*L7+MIN(5,Rules!$B$19)*M7)/(K7+L7+M7)</x:f>
-        <x:v>0.641</x:v>
+        <x:f aca="0">H7*(1+Rules!$B$20*IF(Q7&gt;1,1,0))+I7*(MIN(3,Q7)*K7+MIN(4,Q7)*L7+MIN(5,Q7)*M7+MIN(6,Q7)*P7)/(K7+L7+M7+P7)</x:f>
+        <x:v>0.576</x:v>
       </x:c>
       <x:c r="O7" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A7)</x:f>
         <x:v>36</x:v>
       </x:c>
+      <x:c r="P7" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R7" s="33" t="n">
+        <x:v>0.125</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="10" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="8" t="n">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C8" s="8" t="n">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D8" s="17" t="n">
         <x:v>0.0011</x:v>
@@ -9904,23 +9944,32 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="N8" s="19" t="n">
-        <x:f aca="0">H8*(1+Rules!$B$20)+I8*(3*K8+4*L8+MIN(5,Rules!$B$19)*M8)/(K8+L8+M8)</x:f>
-        <x:v>0.7061999999999999</x:v>
+        <x:f aca="0">H8*(1+Rules!$B$20*IF(Q8&gt;1,1,0))+I8*(MIN(3,Q8)*K8+MIN(4,Q8)*L8+MIN(5,Q8)*M8+MIN(6,Q8)*P8)/(K8+L8+M8+P8)</x:f>
+        <x:v>0.6839999999999999</x:v>
       </x:c>
       <x:c r="O8" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A8)</x:f>
         <x:v>48</x:v>
       </x:c>
+      <x:c r="P8" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R8" s="33" t="n">
+        <x:v>0.1875</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="10" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="8" t="n">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="8" t="n">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D9" s="17" t="n">
         <x:v>0.0012</x:v>
@@ -9957,23 +10006,32 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="N9" s="19" t="n">
-        <x:f aca="0">H9*(1+Rules!$B$20)+I9*(3*K9+4*L9+MIN(5,Rules!$B$19)*M9)/(K9+L9+M9)</x:f>
-        <x:v>0.7735</x:v>
+        <x:f aca="0">H9*(1+Rules!$B$20*IF(Q9&gt;1,1,0))+I9*(MIN(3,Q9)*K9+MIN(4,Q9)*L9+MIN(5,Q9)*M9+MIN(6,Q9)*P9)/(K9+L9+M9+P9)</x:f>
+        <x:v>0.742</x:v>
       </x:c>
       <x:c r="O9" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A9)</x:f>
         <x:v>61</x:v>
       </x:c>
+      <x:c r="P9" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R9" s="33" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="10" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="8" t="n">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C10" s="8" t="n">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D10" s="17" t="n">
         <x:v>0.0012</x:v>
@@ -10010,23 +10068,32 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="N10" s="19" t="n">
-        <x:f aca="0">H10*(1+Rules!$B$20)+I10*(3*K10+4*L10+MIN(5,Rules!$B$19)*M10)/(K10+L10+M10)</x:f>
-        <x:v>0.8432</x:v>
+        <x:f aca="0">H10*(1+Rules!$B$20*IF(Q10&gt;1,1,0))+I10*(MIN(3,Q10)*K10+MIN(4,Q10)*L10+MIN(5,Q10)*M10+MIN(6,Q10)*P10)/(K10+L10+M10+P10)</x:f>
+        <x:v>0.8335999999999999</x:v>
       </x:c>
       <x:c r="O10" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A10)</x:f>
         <x:v>69</x:v>
       </x:c>
+      <x:c r="P10" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R10" s="33" t="n">
+        <x:v>0.3125</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="10" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="8" t="n">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="8" t="n">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D11" s="17" t="n">
         <x:v>0.0013</x:v>
@@ -10063,23 +10130,32 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N11" s="19" t="n">
-        <x:f aca="0">H11*(1+Rules!$B$20)+I11*(3*K11+4*L11+MIN(5,Rules!$B$19)*M11)/(K11+L11+M11)</x:f>
-        <x:v>0.9147</x:v>
+        <x:f aca="0">H11*(1+Rules!$B$20*IF(Q11&gt;1,1,0))+I11*(MIN(3,Q11)*K11+MIN(4,Q11)*L11+MIN(5,Q11)*M11+MIN(6,Q11)*P11)/(K11+L11+M11+P11)</x:f>
+        <x:v>0.9012</x:v>
       </x:c>
       <x:c r="O11" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A11)</x:f>
         <x:v>85</x:v>
       </x:c>
+      <x:c r="P11" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R11" s="33" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="10" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="8" t="n">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C12" s="8" t="n">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D12" s="17" t="n">
         <x:v>0.0013</x:v>
@@ -10116,20 +10192,29 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="N12" s="19" t="n">
-        <x:f aca="0">H12*(1+Rules!$B$20)+I12*(3*K12+4*L12+MIN(5,Rules!$B$19)*M12)/(K12+L12+M12)</x:f>
+        <x:f aca="0">H12*(1+Rules!$B$20*IF(Q12&gt;1,1,0))+I12*(MIN(3,Q12)*K12+MIN(4,Q12)*L12+MIN(5,Q12)*M12+MIN(6,Q12)*P12)/(K12+L12+M12+P12)</x:f>
         <x:v>0.988</x:v>
       </x:c>
       <x:c r="O12" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A12)</x:f>
         <x:v>96</x:v>
       </x:c>
+      <x:c r="P12" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R12" s="33" t="n">
+        <x:v>0.4375</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="10" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="8" t="n">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C13" s="8" t="n">
         <x:v>90</x:v>
@@ -10169,27 +10254,36 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="N13" s="19" t="n">
-        <x:f aca="0">H13*(1+Rules!$B$20)+I13*(3*K13+4*L13+MIN(5,Rules!$B$19)*M13)/(K13+L13+M13)</x:f>
-        <x:v>1.1024</x:v>
+        <x:f aca="0">H13*(1+Rules!$B$20*IF(Q13&gt;1,1,0))+I13*(MIN(3,Q13)*K13+MIN(4,Q13)*L13+MIN(5,Q13)*M13+MIN(6,Q13)*P13)/(K13+L13+M13+P13)</x:f>
+        <x:v>1.1365217391304347</x:v>
       </x:c>
       <x:c r="O13" s="20" t="n">
         <x:f aca="0">COUNTIFS(Affixes!$I$5:$I$104,"&lt;="&amp;A13)</x:f>
         <x:v>100</x:v>
       </x:c>
+      <x:c r="P13" s="8" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q13" s="8" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R13" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="13" t="s">
-        <x:v>520</x:v>
+      <x:c r="A15" s="13" t="str">
+        <x:v>Higher degrees unlock stronger affix tiers and raise the minimum roll percentile. Blue caps: 1/2/2/3/3/4/4/5/6; normal drops still have zero blues.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="13" t="s">
-        <x:v>521</x:v>
+        <x:v>519</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9941c55e0324961"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5e9aed66005470c"/>
 </x:worksheet>
 </file>
 
@@ -10216,53 +10310,53 @@
   <x:sheetData>
     <x:row r="1" ht="17.25" hidden="0" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="s">
         <x:v>524</x:v>
       </x:c>
-      <x:c r="B4" s="7" t="s">
+      <x:c r="D4" s="7" t="s">
         <x:v>525</x:v>
       </x:c>
-      <x:c r="C4" s="7" t="s">
+      <x:c r="E4" s="7" t="s">
         <x:v>526</x:v>
       </x:c>
-      <x:c r="D4" s="7" t="s">
+      <x:c r="F4" s="7" t="s">
         <x:v>527</x:v>
-      </x:c>
-      <x:c r="E4" s="7" t="s">
-        <x:v>528</x:v>
-      </x:c>
-      <x:c r="F4" s="7" t="s">
-        <x:v>529</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
         <x:v>142</x:v>
       </x:c>
       <x:c r="H4" s="7" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="J4" s="7" t="s">
         <x:v>530</x:v>
       </x:c>
-      <x:c r="I4" s="7" t="s">
+      <x:c r="K4" s="7" t="s">
         <x:v>531</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>532</x:v>
-      </x:c>
-      <x:c r="K4" s="7" t="s">
-        <x:v>533</x:v>
       </x:c>
       <x:c r="L4" s="7" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="M4" s="7" t="s">
-        <x:v>534</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="N4" s="7" t="s">
         <x:v>94</x:v>
@@ -10274,30 +10368,30 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="Q4" s="21" t="s">
-        <x:v>535</x:v>
+        <x:v>533</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="10" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="s">
         <x:v>536</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="s">
+      <x:c r="D5" s="10" t="s">
         <x:v>537</x:v>
       </x:c>
-      <x:c r="C5" s="10" t="s">
+      <x:c r="E5" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="s">
+      <x:c r="F5" s="8" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="E5" s="8" t="s">
+      <x:c r="G5" s="9" t="s">
         <x:v>540</x:v>
-      </x:c>
-      <x:c r="F5" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="s">
-        <x:v>542</x:v>
       </x:c>
       <x:c r="H5" s="10" t="n">
         <x:v>1</x:v>
@@ -10312,16 +10406,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L5" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M5" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N5" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O5" s="9" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="P5" s="8" t="s">
         <x:v>169</x:v>
@@ -10332,25 +10426,25 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="10" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B6" s="8" t="s">
-        <x:v>547</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C6" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D6" s="10" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="E6" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D6" s="10" t="s">
+      <x:c r="F6" s="8" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="s">
+      <x:c r="G6" s="9" t="s">
         <x:v>540</x:v>
-      </x:c>
-      <x:c r="F6" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G6" s="9" t="s">
-        <x:v>542</x:v>
       </x:c>
       <x:c r="H6" s="10" t="n">
         <x:v>2</x:v>
@@ -10365,16 +10459,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L6" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M6" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N6" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O6" s="9" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="P6" s="8" t="s">
         <x:v>169</x:v>
@@ -10385,25 +10479,25 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="10" t="s">
-        <x:v>548</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B7" s="8" t="s">
-        <x:v>549</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C7" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="E7" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="F7" s="8" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="s">
+      <x:c r="G7" s="9" t="s">
         <x:v>540</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G7" s="9" t="s">
-        <x:v>542</x:v>
       </x:c>
       <x:c r="H7" s="10" t="n">
         <x:v>3</x:v>
@@ -10418,16 +10512,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L7" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M7" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N7" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O7" s="9" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="P7" s="8" t="s">
         <x:v>169</x:v>
@@ -10438,25 +10532,25 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="10" t="s">
-        <x:v>550</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B8" s="8" t="s">
-        <x:v>551</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="C8" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D8" s="10" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D8" s="10" t="s">
+      <x:c r="F8" s="8" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>540</x:v>
-      </x:c>
-      <x:c r="F8" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="s">
-        <x:v>542</x:v>
       </x:c>
       <x:c r="H8" s="10" t="n">
         <x:v>4</x:v>
@@ -10471,16 +10565,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M8" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N8" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O8" s="9" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="P8" s="8" t="s">
         <x:v>169</x:v>
@@ -10491,25 +10585,25 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="10" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="C9" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="s">
         <x:v>552</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="s">
+      <x:c r="E9" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="s">
         <x:v>553</x:v>
-      </x:c>
-      <x:c r="C9" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D9" s="10" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="E9" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F9" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G9" s="9" t="s">
-        <x:v>555</x:v>
       </x:c>
       <x:c r="H9" s="10" t="n">
         <x:v>1</x:v>
@@ -10524,16 +10618,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L9" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M9" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N9" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O9" s="9" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="P9" s="8" t="s">
         <x:v>169</x:v>
@@ -10544,25 +10638,25 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="10" t="s">
-        <x:v>557</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B10" s="8" t="s">
-        <x:v>558</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="C10" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D10" s="10" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="E10" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D10" s="10" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="E10" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>541</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="G10" s="9" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="H10" s="10" t="n">
         <x:v>2</x:v>
@@ -10577,16 +10671,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L10" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M10" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N10" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O10" s="9" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="P10" s="8" t="s">
         <x:v>169</x:v>
@@ -10597,25 +10691,25 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="10" t="s">
-        <x:v>559</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B11" s="8" t="s">
-        <x:v>560</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="C11" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D11" s="10" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="E11" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D11" s="10" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="E11" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F11" s="8" t="s">
-        <x:v>541</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="G11" s="9" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="H11" s="10" t="n">
         <x:v>3</x:v>
@@ -10630,16 +10724,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L11" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M11" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N11" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O11" s="9" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="P11" s="8" t="s">
         <x:v>169</x:v>
@@ -10650,25 +10744,25 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="10" t="s">
-        <x:v>561</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B12" s="8" t="s">
-        <x:v>562</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C12" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D12" s="10" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D12" s="10" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="E12" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F12" s="8" t="s">
-        <x:v>541</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="G12" s="9" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="H12" s="10" t="n">
         <x:v>4</x:v>
@@ -10683,16 +10777,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L12" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M12" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N12" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O12" s="9" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="P12" s="8" t="s">
         <x:v>169</x:v>
@@ -10703,25 +10797,25 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="10" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B13" s="8" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D13" s="10" t="s">
         <x:v>563</x:v>
       </x:c>
-      <x:c r="B13" s="8" t="s">
+      <x:c r="E13" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F13" s="8" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="C13" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D13" s="10" t="s">
+      <x:c r="G13" s="9" t="s">
         <x:v>565</x:v>
-      </x:c>
-      <x:c r="E13" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F13" s="8" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="G13" s="9" t="s">
-        <x:v>567</x:v>
       </x:c>
       <x:c r="H13" s="10" t="n">
         <x:v>1</x:v>
@@ -10736,16 +10830,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="L13" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M13" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N13" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O13" s="9" t="s">
-        <x:v>568</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="P13" s="8" t="s">
         <x:v>169</x:v>
@@ -10756,25 +10850,25 @@
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="10" t="s">
-        <x:v>569</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B14" s="8" t="s">
-        <x:v>570</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="C14" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D14" s="10" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="E14" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D14" s="10" t="s">
+      <x:c r="F14" s="8" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="s">
         <x:v>565</x:v>
-      </x:c>
-      <x:c r="E14" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F14" s="8" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="G14" s="9" t="s">
-        <x:v>567</x:v>
       </x:c>
       <x:c r="H14" s="10" t="n">
         <x:v>2</x:v>
@@ -10789,16 +10883,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L14" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M14" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N14" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O14" s="9" t="s">
-        <x:v>568</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="P14" s="8" t="s">
         <x:v>169</x:v>
@@ -10809,25 +10903,25 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="10" t="s">
-        <x:v>571</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B15" s="8" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="C15" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D15" s="10" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D15" s="10" t="s">
+      <x:c r="F15" s="8" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="s">
         <x:v>565</x:v>
-      </x:c>
-      <x:c r="E15" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F15" s="8" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="G15" s="9" t="s">
-        <x:v>567</x:v>
       </x:c>
       <x:c r="H15" s="10" t="n">
         <x:v>3</x:v>
@@ -10842,16 +10936,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L15" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M15" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N15" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O15" s="9" t="s">
-        <x:v>568</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="P15" s="8" t="s">
         <x:v>169</x:v>
@@ -10862,25 +10956,25 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="10" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="s">
         <x:v>573</x:v>
       </x:c>
-      <x:c r="B16" s="8" t="s">
+      <x:c r="E16" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="s">
         <x:v>574</x:v>
       </x:c>
-      <x:c r="C16" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D16" s="10" t="s">
+      <x:c r="G16" s="9" t="s">
         <x:v>575</x:v>
-      </x:c>
-      <x:c r="E16" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F16" s="8" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G16" s="9" t="s">
-        <x:v>577</x:v>
       </x:c>
       <x:c r="H16" s="10" t="n">
         <x:v>1</x:v>
@@ -10895,16 +10989,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L16" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M16" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N16" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O16" s="9" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="P16" s="8" t="s">
         <x:v>169</x:v>
@@ -10915,25 +11009,25 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="10" t="s">
-        <x:v>580</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>581</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C17" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="E17" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D17" s="10" t="s">
+      <x:c r="F17" s="8" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="s">
         <x:v>575</x:v>
-      </x:c>
-      <x:c r="E17" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F17" s="8" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G17" s="9" t="s">
-        <x:v>577</x:v>
       </x:c>
       <x:c r="H17" s="10" t="n">
         <x:v>2</x:v>
@@ -10948,16 +11042,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L17" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M17" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N17" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O17" s="9" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="P17" s="8" t="s">
         <x:v>169</x:v>
@@ -10968,25 +11062,25 @@
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="10" t="s">
-        <x:v>582</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>583</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="C18" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="E18" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D18" s="10" t="s">
+      <x:c r="F18" s="8" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="s">
         <x:v>575</x:v>
-      </x:c>
-      <x:c r="E18" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G18" s="9" t="s">
-        <x:v>577</x:v>
       </x:c>
       <x:c r="H18" s="10" t="n">
         <x:v>3</x:v>
@@ -11001,16 +11095,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L18" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M18" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N18" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O18" s="9" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="P18" s="8" t="s">
         <x:v>169</x:v>
@@ -11021,25 +11115,25 @@
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="10" t="s">
-        <x:v>584</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>585</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="C19" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="E19" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D19" s="10" t="s">
+      <x:c r="F19" s="8" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G19" s="9" t="s">
         <x:v>575</x:v>
-      </x:c>
-      <x:c r="E19" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F19" s="8" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G19" s="9" t="s">
-        <x:v>577</x:v>
       </x:c>
       <x:c r="H19" s="10" t="n">
         <x:v>4</x:v>
@@ -11054,16 +11148,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="L19" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M19" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N19" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O19" s="9" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="P19" s="8" t="s">
         <x:v>169</x:v>
@@ -11074,25 +11168,25 @@
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="10" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="C20" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="s">
         <x:v>586</x:v>
       </x:c>
-      <x:c r="B20" s="8" t="s">
+      <x:c r="E20" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F20" s="8" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="s">
         <x:v>587</x:v>
-      </x:c>
-      <x:c r="C20" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D20" s="10" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="E20" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F20" s="8" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G20" s="9" t="s">
-        <x:v>589</x:v>
       </x:c>
       <x:c r="H20" s="10" t="n">
         <x:v>1</x:v>
@@ -11107,16 +11201,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L20" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M20" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N20" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O20" s="9" t="s">
-        <x:v>590</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="P20" s="8" t="s">
         <x:v>169</x:v>
@@ -11127,25 +11221,25 @@
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="10" t="s">
-        <x:v>591</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B21" s="8" t="s">
-        <x:v>592</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="C21" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="E21" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D21" s="10" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="E21" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F21" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G21" s="9" t="s">
-        <x:v>589</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="H21" s="10" t="n">
         <x:v>2</x:v>
@@ -11160,16 +11254,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L21" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M21" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N21" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O21" s="9" t="s">
-        <x:v>590</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="P21" s="8" t="s">
         <x:v>169</x:v>
@@ -11180,25 +11274,25 @@
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="10" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B22" s="8" t="s">
-        <x:v>594</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="C22" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="E22" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D22" s="10" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="E22" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F22" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G22" s="9" t="s">
-        <x:v>589</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="H22" s="10" t="n">
         <x:v>3</x:v>
@@ -11213,16 +11307,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L22" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M22" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N22" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O22" s="9" t="s">
-        <x:v>590</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="P22" s="8" t="s">
         <x:v>169</x:v>
@@ -11233,25 +11327,25 @@
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="10" t="s">
-        <x:v>595</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B23" s="8" t="s">
-        <x:v>596</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="C23" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="E23" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D23" s="10" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="E23" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F23" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G23" s="9" t="s">
-        <x:v>589</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="H23" s="10" t="n">
         <x:v>4</x:v>
@@ -11266,16 +11360,16 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="L23" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M23" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N23" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O23" s="9" t="s">
-        <x:v>590</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="P23" s="8" t="s">
         <x:v>169</x:v>
@@ -11286,25 +11380,25 @@
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="10" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="C24" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="s">
         <x:v>597</x:v>
       </x:c>
-      <x:c r="B24" s="8" t="s">
+      <x:c r="E24" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F24" s="8" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="s">
         <x:v>598</x:v>
-      </x:c>
-      <x:c r="C24" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D24" s="10" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="E24" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F24" s="8" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G24" s="9" t="s">
-        <x:v>600</x:v>
       </x:c>
       <x:c r="H24" s="10" t="n">
         <x:v>1</x:v>
@@ -11319,16 +11413,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M24" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N24" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O24" s="9" t="s">
-        <x:v>601</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="P24" s="8" t="s">
         <x:v>169</x:v>
@@ -11339,25 +11433,25 @@
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="10" t="s">
-        <x:v>602</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B25" s="8" t="s">
-        <x:v>603</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="C25" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="E25" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D25" s="10" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="E25" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F25" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G25" s="9" t="s">
-        <x:v>600</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="H25" s="10" t="n">
         <x:v>2</x:v>
@@ -11372,16 +11466,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L25" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M25" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N25" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O25" s="9" t="s">
-        <x:v>601</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="P25" s="8" t="s">
         <x:v>169</x:v>
@@ -11392,25 +11486,25 @@
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="10" t="s">
-        <x:v>604</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B26" s="8" t="s">
-        <x:v>605</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="C26" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D26" s="10" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="E26" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D26" s="10" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="E26" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F26" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G26" s="9" t="s">
-        <x:v>600</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="H26" s="10" t="n">
         <x:v>3</x:v>
@@ -11425,16 +11519,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="L26" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M26" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N26" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O26" s="9" t="s">
-        <x:v>601</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="P26" s="8" t="s">
         <x:v>169</x:v>
@@ -11445,25 +11539,25 @@
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="10" t="s">
-        <x:v>606</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B27" s="8" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C27" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D27" s="10" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="E27" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D27" s="10" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="E27" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F27" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G27" s="9" t="s">
-        <x:v>600</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="H27" s="10" t="n">
         <x:v>4</x:v>
@@ -11478,16 +11572,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="L27" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M27" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N27" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O27" s="9" t="s">
-        <x:v>601</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="P27" s="8" t="s">
         <x:v>169</x:v>
@@ -11498,25 +11592,25 @@
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="10" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B28" s="8" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="C28" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D28" s="10" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="B28" s="8" t="s">
+      <x:c r="E28" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F28" s="8" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="s">
         <x:v>609</x:v>
-      </x:c>
-      <x:c r="C28" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D28" s="10" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="E28" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F28" s="8" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G28" s="9" t="s">
-        <x:v>611</x:v>
       </x:c>
       <x:c r="H28" s="10" t="n">
         <x:v>1</x:v>
@@ -11531,16 +11625,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="L28" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M28" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N28" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O28" s="9" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="P28" s="8" t="s">
         <x:v>169</x:v>
@@ -11551,25 +11645,25 @@
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="10" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B29" s="8" t="s">
-        <x:v>614</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="C29" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D29" s="10" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="E29" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D29" s="10" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="E29" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F29" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G29" s="9" t="s">
-        <x:v>611</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="H29" s="10" t="n">
         <x:v>2</x:v>
@@ -11584,16 +11678,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L29" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M29" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N29" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O29" s="9" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="P29" s="8" t="s">
         <x:v>169</x:v>
@@ -11604,25 +11698,25 @@
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" s="10" t="s">
-        <x:v>615</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B30" s="8" t="s">
-        <x:v>616</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="C30" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D30" s="10" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="E30" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D30" s="10" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="E30" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F30" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G30" s="9" t="s">
-        <x:v>611</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="H30" s="10" t="n">
         <x:v>3</x:v>
@@ -11637,16 +11731,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="L30" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M30" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N30" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O30" s="9" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="P30" s="8" t="s">
         <x:v>169</x:v>
@@ -11657,25 +11751,25 @@
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="10" t="s">
-        <x:v>617</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="B31" s="8" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="C31" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D31" s="10" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="E31" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D31" s="10" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="E31" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F31" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G31" s="9" t="s">
-        <x:v>611</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="H31" s="10" t="n">
         <x:v>4</x:v>
@@ -11690,16 +11784,16 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="L31" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M31" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N31" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O31" s="9" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="P31" s="8" t="s">
         <x:v>169</x:v>
@@ -11710,25 +11804,25 @@
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="10" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="B32" s="8" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="C32" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D32" s="10" t="s">
         <x:v>619</x:v>
       </x:c>
-      <x:c r="B32" s="8" t="s">
+      <x:c r="E32" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F32" s="8" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="s">
         <x:v>620</x:v>
-      </x:c>
-      <x:c r="C32" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D32" s="10" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="E32" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F32" s="8" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="G32" s="9" t="s">
-        <x:v>622</x:v>
       </x:c>
       <x:c r="H32" s="10" t="n">
         <x:v>1</x:v>
@@ -11743,16 +11837,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="L32" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M32" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N32" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O32" s="9" t="s">
-        <x:v>623</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="P32" s="8" t="s">
         <x:v>169</x:v>
@@ -11763,25 +11857,25 @@
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="10" t="s">
-        <x:v>624</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="B33" s="8" t="s">
-        <x:v>625</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C33" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D33" s="10" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="E33" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D33" s="10" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="E33" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F33" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G33" s="9" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="H33" s="10" t="n">
         <x:v>2</x:v>
@@ -11796,16 +11890,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L33" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M33" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N33" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O33" s="9" t="s">
-        <x:v>623</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="P33" s="8" t="s">
         <x:v>169</x:v>
@@ -11816,25 +11910,25 @@
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="10" t="s">
-        <x:v>626</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B34" s="8" t="s">
-        <x:v>627</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="C34" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D34" s="10" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="E34" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D34" s="10" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="E34" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F34" s="8" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="G34" s="9" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="H34" s="10" t="n">
         <x:v>3</x:v>
@@ -11849,16 +11943,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L34" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M34" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N34" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O34" s="9" t="s">
-        <x:v>623</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="P34" s="8" t="s">
         <x:v>169</x:v>
@@ -11869,25 +11963,25 @@
     </x:row>
     <x:row r="35" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A35" s="10" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="B35" s="8" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="C35" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D35" s="10" t="s">
         <x:v>628</x:v>
       </x:c>
-      <x:c r="B35" s="8" t="s">
+      <x:c r="E35" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F35" s="8" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="G35" s="9" t="s">
         <x:v>629</x:v>
-      </x:c>
-      <x:c r="C35" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D35" s="10" t="s">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="E35" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F35" s="8" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="G35" s="9" t="s">
-        <x:v>631</x:v>
       </x:c>
       <x:c r="H35" s="10" t="n">
         <x:v>1</x:v>
@@ -11902,16 +11996,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L35" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M35" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N35" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O35" s="9" t="s">
-        <x:v>632</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="P35" s="8" t="s">
         <x:v>169</x:v>
@@ -11922,25 +12016,25 @@
     </x:row>
     <x:row r="36" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A36" s="10" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="B36" s="8" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C36" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D36" s="10" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="E36" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D36" s="10" t="s">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="E36" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F36" s="8" t="s">
-        <x:v>566</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="G36" s="9" t="s">
-        <x:v>631</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="H36" s="10" t="n">
         <x:v>2</x:v>
@@ -11955,16 +12049,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L36" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M36" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N36" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O36" s="9" t="s">
-        <x:v>632</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="P36" s="8" t="s">
         <x:v>169</x:v>
@@ -11975,25 +12069,25 @@
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="10" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="C37" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D37" s="10" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="E37" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F37" s="8" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="G37" s="9" t="s">
         <x:v>635</x:v>
-      </x:c>
-      <x:c r="B37" s="8" t="s">
-        <x:v>636</x:v>
-      </x:c>
-      <x:c r="C37" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D37" s="10" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="E37" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F37" s="8" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="G37" s="9" t="s">
-        <x:v>637</x:v>
       </x:c>
       <x:c r="H37" s="10" t="n">
         <x:v>1</x:v>
@@ -12008,16 +12102,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L37" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M37" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N37" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O37" s="9" t="s">
-        <x:v>638</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="P37" s="8" t="s">
         <x:v>169</x:v>
@@ -12028,25 +12122,25 @@
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="10" t="s">
-        <x:v>639</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="B38" s="8" t="s">
-        <x:v>640</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="C38" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D38" s="10" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="E38" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D38" s="10" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="E38" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F38" s="8" t="s">
-        <x:v>566</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="G38" s="9" t="s">
-        <x:v>637</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="H38" s="10" t="n">
         <x:v>2</x:v>
@@ -12061,16 +12155,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L38" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M38" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N38" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O38" s="9" t="s">
-        <x:v>638</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="P38" s="8" t="s">
         <x:v>169</x:v>
@@ -12081,25 +12175,25 @@
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="10" t="s">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="B39" s="8" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="C39" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D39" s="10" t="s">
         <x:v>641</x:v>
       </x:c>
-      <x:c r="B39" s="8" t="s">
+      <x:c r="E39" s="8" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F39" s="8" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="G39" s="9" t="s">
         <x:v>642</x:v>
-      </x:c>
-      <x:c r="C39" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D39" s="10" t="s">
-        <x:v>643</x:v>
-      </x:c>
-      <x:c r="E39" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="F39" s="8" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="G39" s="9" t="s">
-        <x:v>644</x:v>
       </x:c>
       <x:c r="H39" s="10" t="n">
         <x:v>1</x:v>
@@ -12114,16 +12208,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L39" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M39" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N39" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O39" s="9" t="s">
-        <x:v>645</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="P39" s="8" t="s">
         <x:v>169</x:v>
@@ -12134,25 +12228,25 @@
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="10" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="B40" s="8" t="s">
-        <x:v>647</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="C40" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D40" s="10" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="E40" s="8" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="D40" s="10" t="s">
-        <x:v>643</x:v>
-      </x:c>
-      <x:c r="E40" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
       <x:c r="F40" s="8" t="s">
-        <x:v>566</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="G40" s="9" t="s">
-        <x:v>644</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="H40" s="10" t="n">
         <x:v>2</x:v>
@@ -12167,16 +12261,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L40" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M40" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N40" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O40" s="9" t="s">
-        <x:v>645</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="P40" s="8" t="s">
         <x:v>169</x:v>
@@ -12187,25 +12281,25 @@
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="10" t="s">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="B41" s="8" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="C41" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D41" s="10" t="s">
         <x:v>648</x:v>
-      </x:c>
-      <x:c r="B41" s="8" t="s">
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="C41" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D41" s="10" t="s">
-        <x:v>650</x:v>
       </x:c>
       <x:c r="E41" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F41" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G41" s="9" t="s">
-        <x:v>652</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="H41" s="10" t="n">
         <x:v>1</x:v>
@@ -12220,16 +12314,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L41" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M41" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N41" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O41" s="9" t="s">
-        <x:v>653</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="P41" s="8" t="s">
         <x:v>169</x:v>
@@ -12240,25 +12334,25 @@
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="10" t="s">
-        <x:v>654</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="B42" s="8" t="s">
-        <x:v>655</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="C42" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D42" s="10" t="s">
-        <x:v>650</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E42" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F42" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G42" s="9" t="s">
-        <x:v>652</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="H42" s="10" t="n">
         <x:v>2</x:v>
@@ -12273,16 +12367,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L42" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M42" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N42" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O42" s="9" t="s">
-        <x:v>653</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="P42" s="8" t="s">
         <x:v>169</x:v>
@@ -12293,25 +12387,25 @@
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="10" t="s">
-        <x:v>656</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="B43" s="8" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="C43" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D43" s="10" t="s">
-        <x:v>650</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E43" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F43" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G43" s="9" t="s">
-        <x:v>652</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="H43" s="10" t="n">
         <x:v>3</x:v>
@@ -12326,16 +12420,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L43" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M43" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N43" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O43" s="9" t="s">
-        <x:v>653</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="P43" s="8" t="s">
         <x:v>169</x:v>
@@ -12346,25 +12440,25 @@
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="10" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B44" s="8" t="s">
-        <x:v>659</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="C44" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D44" s="10" t="s">
-        <x:v>650</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E44" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F44" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G44" s="9" t="s">
-        <x:v>652</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="H44" s="10" t="n">
         <x:v>4</x:v>
@@ -12379,16 +12473,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="L44" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M44" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N44" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O44" s="9" t="s">
-        <x:v>653</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="P44" s="8" t="s">
         <x:v>169</x:v>
@@ -12399,25 +12493,25 @@
     </x:row>
     <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="10" t="s">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="B45" s="8" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="C45" s="10" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D45" s="10" t="s">
         <x:v>660</x:v>
-      </x:c>
-      <x:c r="B45" s="8" t="s">
-        <x:v>661</x:v>
-      </x:c>
-      <x:c r="C45" s="10" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="D45" s="10" t="s">
-        <x:v>662</x:v>
       </x:c>
       <x:c r="E45" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F45" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G45" s="9" t="s">
-        <x:v>663</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="H45" s="10" t="n">
         <x:v>1</x:v>
@@ -12432,16 +12526,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L45" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M45" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N45" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O45" s="9" t="s">
-        <x:v>664</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="P45" s="8" t="s">
         <x:v>217</x:v>
@@ -12452,25 +12546,25 @@
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
       <x:c r="A46" s="10" t="s">
-        <x:v>665</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="B46" s="8" t="s">
-        <x:v>666</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="C46" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D46" s="10" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="E46" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F46" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G46" s="9" t="s">
-        <x:v>663</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="H46" s="10" t="n">
         <x:v>2</x:v>
@@ -12485,16 +12579,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="L46" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M46" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N46" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O46" s="9" t="s">
-        <x:v>664</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="P46" s="8" t="s">
         <x:v>217</x:v>
@@ -12505,25 +12599,25 @@
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="10" t="s">
-        <x:v>667</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="B47" s="8" t="s">
-        <x:v>668</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="C47" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D47" s="10" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="E47" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F47" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G47" s="9" t="s">
-        <x:v>663</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="H47" s="10" t="n">
         <x:v>3</x:v>
@@ -12538,16 +12632,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L47" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M47" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N47" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O47" s="9" t="s">
-        <x:v>664</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="P47" s="8" t="s">
         <x:v>217</x:v>
@@ -12558,25 +12652,25 @@
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="10" t="s">
-        <x:v>669</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="B48" s="8" t="s">
-        <x:v>670</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="C48" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D48" s="10" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="E48" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F48" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G48" s="9" t="s">
-        <x:v>663</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="H48" s="10" t="n">
         <x:v>4</x:v>
@@ -12591,16 +12685,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L48" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M48" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N48" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O48" s="9" t="s">
-        <x:v>664</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="P48" s="8" t="s">
         <x:v>217</x:v>
@@ -12611,13 +12705,13 @@
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
       <x:c r="A49" s="10" t="s">
-        <x:v>671</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="B49" s="8" t="s">
-        <x:v>672</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="C49" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D49" s="10" t="s">
         <x:v>270</x:v>
@@ -12626,10 +12720,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="F49" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G49" s="9" t="s">
-        <x:v>673</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="H49" s="10" t="n">
         <x:v>1</x:v>
@@ -12644,16 +12738,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L49" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M49" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N49" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O49" s="9" t="s">
-        <x:v>674</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="P49" s="8" t="s">
         <x:v>217</x:v>
@@ -12664,13 +12758,13 @@
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="10" t="s">
-        <x:v>675</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="B50" s="8" t="s">
-        <x:v>676</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="C50" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D50" s="10" t="s">
         <x:v>270</x:v>
@@ -12679,10 +12773,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="F50" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G50" s="9" t="s">
-        <x:v>673</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="H50" s="10" t="n">
         <x:v>2</x:v>
@@ -12697,16 +12791,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L50" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M50" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N50" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O50" s="9" t="s">
-        <x:v>674</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="P50" s="8" t="s">
         <x:v>217</x:v>
@@ -12717,13 +12811,13 @@
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="10" t="s">
-        <x:v>677</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B51" s="8" t="s">
-        <x:v>678</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C51" s="10" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D51" s="10" t="s">
         <x:v>270</x:v>
@@ -12732,10 +12826,10 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="F51" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G51" s="9" t="s">
-        <x:v>673</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="H51" s="10" t="n">
         <x:v>3</x:v>
@@ -12750,16 +12844,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="L51" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="M51" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N51" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O51" s="9" t="s">
-        <x:v>674</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="P51" s="8" t="s">
         <x:v>217</x:v>
@@ -12770,25 +12864,25 @@
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="10" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="B52" s="8" t="s">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="C52" s="10" t="s">
         <x:v>679</x:v>
       </x:c>
-      <x:c r="B52" s="8" t="s">
+      <x:c r="D52" s="10" t="s">
         <x:v>680</x:v>
       </x:c>
-      <x:c r="C52" s="10" t="s">
+      <x:c r="E52" s="8" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="F52" s="8" t="s">
         <x:v>681</x:v>
       </x:c>
-      <x:c r="D52" s="10" t="s">
+      <x:c r="G52" s="9" t="s">
         <x:v>682</x:v>
-      </x:c>
-      <x:c r="E52" s="8" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="F52" s="8" t="s">
-        <x:v>683</x:v>
-      </x:c>
-      <x:c r="G52" s="9" t="s">
-        <x:v>684</x:v>
       </x:c>
       <x:c r="H52" s="10" t="n">
         <x:v>1</x:v>
@@ -12803,16 +12897,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L52" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M52" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N52" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O52" s="9" t="s">
-        <x:v>685</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="P52" s="8" t="s">
         <x:v>169</x:v>
@@ -12823,25 +12917,25 @@
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="10" t="s">
-        <x:v>686</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="B53" s="8" t="s">
-        <x:v>687</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="C53" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D53" s="10" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="E53" s="8" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="F53" s="8" t="s">
         <x:v>681</x:v>
       </x:c>
-      <x:c r="D53" s="10" t="s">
+      <x:c r="G53" s="9" t="s">
         <x:v>682</x:v>
-      </x:c>
-      <x:c r="E53" s="8" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="F53" s="8" t="s">
-        <x:v>683</x:v>
-      </x:c>
-      <x:c r="G53" s="9" t="s">
-        <x:v>684</x:v>
       </x:c>
       <x:c r="H53" s="10" t="n">
         <x:v>2</x:v>
@@ -12856,16 +12950,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L53" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M53" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N53" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O53" s="9" t="s">
-        <x:v>685</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="P53" s="8" t="s">
         <x:v>169</x:v>
@@ -12876,25 +12970,25 @@
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="10" t="s">
-        <x:v>688</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="B54" s="8" t="s">
-        <x:v>689</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="C54" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D54" s="10" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="E54" s="8" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="F54" s="8" t="s">
         <x:v>681</x:v>
       </x:c>
-      <x:c r="D54" s="10" t="s">
+      <x:c r="G54" s="9" t="s">
         <x:v>682</x:v>
-      </x:c>
-      <x:c r="E54" s="8" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="F54" s="8" t="s">
-        <x:v>683</x:v>
-      </x:c>
-      <x:c r="G54" s="9" t="s">
-        <x:v>684</x:v>
       </x:c>
       <x:c r="H54" s="10" t="n">
         <x:v>3</x:v>
@@ -12909,16 +13003,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L54" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M54" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N54" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O54" s="9" t="s">
-        <x:v>685</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="P54" s="8" t="s">
         <x:v>169</x:v>
@@ -12929,25 +13023,25 @@
     </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
       <x:c r="A55" s="10" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="B55" s="8" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="C55" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D55" s="10" t="s">
         <x:v>690</x:v>
       </x:c>
-      <x:c r="B55" s="8" t="s">
+      <x:c r="E55" s="8" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="F55" s="8" t="s">
         <x:v>691</x:v>
       </x:c>
-      <x:c r="C55" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D55" s="10" t="s">
+      <x:c r="G55" s="9" t="s">
         <x:v>692</x:v>
-      </x:c>
-      <x:c r="E55" s="8" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="F55" s="8" t="s">
-        <x:v>693</x:v>
-      </x:c>
-      <x:c r="G55" s="9" t="s">
-        <x:v>694</x:v>
       </x:c>
       <x:c r="H55" s="10" t="n">
         <x:v>1</x:v>
@@ -12962,16 +13056,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L55" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M55" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N55" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O55" s="9" t="s">
-        <x:v>695</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="P55" s="8" t="s">
         <x:v>217</x:v>
@@ -12982,25 +13076,25 @@
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="10" t="s">
-        <x:v>696</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="B56" s="8" t="s">
-        <x:v>697</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="C56" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D56" s="10" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="E56" s="8" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="F56" s="8" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="G56" s="9" t="s">
         <x:v>692</x:v>
-      </x:c>
-      <x:c r="E56" s="8" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="F56" s="8" t="s">
-        <x:v>693</x:v>
-      </x:c>
-      <x:c r="G56" s="9" t="s">
-        <x:v>694</x:v>
       </x:c>
       <x:c r="H56" s="10" t="n">
         <x:v>2</x:v>
@@ -13015,16 +13109,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L56" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M56" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N56" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O56" s="9" t="s">
-        <x:v>695</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="P56" s="8" t="s">
         <x:v>217</x:v>
@@ -13035,25 +13129,25 @@
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="10" t="s">
-        <x:v>698</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="B57" s="8" t="s">
-        <x:v>699</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C57" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D57" s="10" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="E57" s="8" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="F57" s="8" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="G57" s="9" t="s">
         <x:v>692</x:v>
-      </x:c>
-      <x:c r="E57" s="8" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="F57" s="8" t="s">
-        <x:v>693</x:v>
-      </x:c>
-      <x:c r="G57" s="9" t="s">
-        <x:v>694</x:v>
       </x:c>
       <x:c r="H57" s="10" t="n">
         <x:v>3</x:v>
@@ -13068,16 +13162,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L57" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M57" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N57" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O57" s="9" t="s">
-        <x:v>695</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="P57" s="8" t="s">
         <x:v>217</x:v>
@@ -13088,25 +13182,25 @@
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="10" t="s">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="B58" s="8" t="s">
+        <x:v>699</x:v>
+      </x:c>
+      <x:c r="C58" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D58" s="10" t="s">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="B58" s="8" t="s">
+      <x:c r="E58" s="8" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="F58" s="8" t="s">
         <x:v>701</x:v>
       </x:c>
-      <x:c r="C58" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D58" s="10" t="s">
+      <x:c r="G58" s="9" t="s">
         <x:v>702</x:v>
-      </x:c>
-      <x:c r="E58" s="8" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="F58" s="8" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="G58" s="9" t="s">
-        <x:v>704</x:v>
       </x:c>
       <x:c r="H58" s="10" t="n">
         <x:v>1</x:v>
@@ -13121,16 +13215,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L58" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M58" s="8" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="N58" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O58" s="9" t="s">
-        <x:v>705</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="P58" s="8" t="s">
         <x:v>217</x:v>
@@ -13141,25 +13235,25 @@
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="10" t="s">
-        <x:v>706</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="B59" s="8" t="s">
-        <x:v>707</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="C59" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D59" s="10" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="E59" s="8" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="F59" s="8" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="G59" s="9" t="s">
         <x:v>702</x:v>
-      </x:c>
-      <x:c r="E59" s="8" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="F59" s="8" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="G59" s="9" t="s">
-        <x:v>704</x:v>
       </x:c>
       <x:c r="H59" s="10" t="n">
         <x:v>2</x:v>
@@ -13174,16 +13268,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L59" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M59" s="8" t="n">
         <x:v>45</x:v>
       </x:c>
       <x:c r="N59" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O59" s="9" t="s">
-        <x:v>705</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="P59" s="8" t="s">
         <x:v>217</x:v>
@@ -13194,25 +13288,25 @@
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="10" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="B60" s="8" t="s">
+        <x:v>707</x:v>
+      </x:c>
+      <x:c r="C60" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D60" s="10" t="s">
         <x:v>708</x:v>
-      </x:c>
-      <x:c r="B60" s="8" t="s">
-        <x:v>709</x:v>
-      </x:c>
-      <x:c r="C60" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D60" s="10" t="s">
-        <x:v>710</x:v>
       </x:c>
       <x:c r="E60" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F60" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G60" s="9" t="s">
-        <x:v>711</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="H60" s="10" t="n">
         <x:v>1</x:v>
@@ -13227,13 +13321,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L60" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M60" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N60" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O60" s="9" t="s">
         <x:v>368</x:v>
@@ -13247,25 +13341,25 @@
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="10" t="s">
-        <x:v>712</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B61" s="8" t="s">
-        <x:v>713</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="C61" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D61" s="10" t="s">
-        <x:v>710</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="E61" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F61" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G61" s="9" t="s">
-        <x:v>711</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="H61" s="10" t="n">
         <x:v>2</x:v>
@@ -13280,13 +13374,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L61" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M61" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N61" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O61" s="9" t="s">
         <x:v>368</x:v>
@@ -13300,25 +13394,25 @@
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="10" t="s">
-        <x:v>714</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B62" s="8" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="C62" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D62" s="10" t="s">
-        <x:v>710</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="E62" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F62" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G62" s="9" t="s">
-        <x:v>711</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="H62" s="10" t="n">
         <x:v>3</x:v>
@@ -13333,13 +13427,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L62" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M62" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N62" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O62" s="9" t="s">
         <x:v>368</x:v>
@@ -13353,25 +13447,25 @@
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
       <x:c r="A63" s="10" t="s">
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="B63" s="8" t="s">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="C63" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D63" s="10" t="s">
         <x:v>716</x:v>
-      </x:c>
-      <x:c r="B63" s="8" t="s">
-        <x:v>717</x:v>
-      </x:c>
-      <x:c r="C63" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D63" s="10" t="s">
-        <x:v>718</x:v>
       </x:c>
       <x:c r="E63" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F63" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G63" s="9" t="s">
-        <x:v>719</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="H63" s="10" t="n">
         <x:v>1</x:v>
@@ -13386,16 +13480,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L63" s="8" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="M63" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N63" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O63" s="9" t="s">
-        <x:v>720</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="P63" s="8" t="s">
         <x:v>217</x:v>
@@ -13406,25 +13500,25 @@
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="10" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B64" s="8" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="C64" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D64" s="10" t="s">
-        <x:v>718</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="E64" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F64" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G64" s="9" t="s">
-        <x:v>719</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="H64" s="10" t="n">
         <x:v>2</x:v>
@@ -13439,16 +13533,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="L64" s="8" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="M64" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N64" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O64" s="9" t="s">
-        <x:v>720</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="P64" s="8" t="s">
         <x:v>217</x:v>
@@ -13459,25 +13553,25 @@
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="10" t="s">
-        <x:v>723</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="B65" s="8" t="s">
-        <x:v>724</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="C65" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D65" s="10" t="s">
-        <x:v>718</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="E65" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F65" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G65" s="9" t="s">
-        <x:v>719</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="H65" s="10" t="n">
         <x:v>3</x:v>
@@ -13492,16 +13586,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="L65" s="8" t="s">
-        <x:v>662</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="M65" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N65" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O65" s="9" t="s">
-        <x:v>720</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="P65" s="8" t="s">
         <x:v>217</x:v>
@@ -13512,25 +13606,25 @@
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="10" t="s">
+        <x:v>723</x:v>
+      </x:c>
+      <x:c r="B66" s="8" t="s">
+        <x:v>724</x:v>
+      </x:c>
+      <x:c r="C66" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D66" s="10" t="s">
         <x:v>725</x:v>
-      </x:c>
-      <x:c r="B66" s="8" t="s">
-        <x:v>726</x:v>
-      </x:c>
-      <x:c r="C66" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D66" s="10" t="s">
-        <x:v>727</x:v>
       </x:c>
       <x:c r="E66" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F66" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G66" s="9" t="s">
-        <x:v>728</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H66" s="10" t="n">
         <x:v>1</x:v>
@@ -13545,16 +13639,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L66" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M66" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N66" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O66" s="9" t="s">
-        <x:v>729</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="P66" s="8" t="s">
         <x:v>217</x:v>
@@ -13565,25 +13659,25 @@
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="10" t="s">
-        <x:v>730</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B67" s="8" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="C67" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D67" s="10" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E67" s="8" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F67" s="8" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="G67" s="9" t="s">
-        <x:v>728</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="H67" s="10" t="n">
         <x:v>2</x:v>
@@ -13598,16 +13692,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L67" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M67" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N67" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O67" s="9" t="s">
-        <x:v>729</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="P67" s="8" t="s">
         <x:v>217</x:v>
@@ -13618,25 +13712,25 @@
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="10" t="s">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="B68" s="8" t="s">
+        <x:v>731</x:v>
+      </x:c>
+      <x:c r="C68" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D68" s="10" t="s">
         <x:v>732</x:v>
-      </x:c>
-      <x:c r="B68" s="8" t="s">
-        <x:v>733</x:v>
-      </x:c>
-      <x:c r="C68" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D68" s="10" t="s">
-        <x:v>734</x:v>
       </x:c>
       <x:c r="E68" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F68" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G68" s="9" t="s">
-        <x:v>735</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="H68" s="10" t="n">
         <x:v>1</x:v>
@@ -13660,7 +13754,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="O68" s="9" t="s">
-        <x:v>736</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="P68" s="8" t="s">
         <x:v>169</x:v>
@@ -13671,25 +13765,25 @@
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="10" t="s">
-        <x:v>737</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B69" s="8" t="s">
-        <x:v>738</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="C69" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D69" s="10" t="s">
-        <x:v>734</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="E69" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F69" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G69" s="9" t="s">
-        <x:v>735</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="H69" s="10" t="n">
         <x:v>2</x:v>
@@ -13713,7 +13807,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="O69" s="9" t="s">
-        <x:v>736</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="P69" s="8" t="s">
         <x:v>169</x:v>
@@ -13724,25 +13818,25 @@
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="10" t="s">
+        <x:v>737</x:v>
+      </x:c>
+      <x:c r="B70" s="8" t="s">
+        <x:v>738</x:v>
+      </x:c>
+      <x:c r="C70" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D70" s="10" t="s">
         <x:v>739</x:v>
-      </x:c>
-      <x:c r="B70" s="8" t="s">
-        <x:v>740</x:v>
-      </x:c>
-      <x:c r="C70" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D70" s="10" t="s">
-        <x:v>741</x:v>
       </x:c>
       <x:c r="E70" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F70" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G70" s="9" t="s">
-        <x:v>742</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="H70" s="10" t="n">
         <x:v>1</x:v>
@@ -13766,7 +13860,7 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="O70" s="9" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="P70" s="8" t="s">
         <x:v>169</x:v>
@@ -13777,25 +13871,25 @@
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="10" t="s">
-        <x:v>744</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B71" s="8" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="C71" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D71" s="10" t="s">
-        <x:v>741</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="E71" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F71" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G71" s="9" t="s">
-        <x:v>742</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="H71" s="10" t="n">
         <x:v>2</x:v>
@@ -13819,7 +13913,7 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="O71" s="9" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="P71" s="8" t="s">
         <x:v>169</x:v>
@@ -13830,25 +13924,25 @@
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="10" t="s">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="B72" s="8" t="s">
+        <x:v>745</x:v>
+      </x:c>
+      <x:c r="C72" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D72" s="10" t="s">
         <x:v>746</x:v>
-      </x:c>
-      <x:c r="B72" s="8" t="s">
-        <x:v>747</x:v>
-      </x:c>
-      <x:c r="C72" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D72" s="10" t="s">
-        <x:v>748</x:v>
       </x:c>
       <x:c r="E72" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F72" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G72" s="9" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="H72" s="10" t="n">
         <x:v>1</x:v>
@@ -13872,7 +13966,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="O72" s="9" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="P72" s="8" t="s">
         <x:v>169</x:v>
@@ -13883,25 +13977,25 @@
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="10" t="s">
-        <x:v>750</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="B73" s="8" t="s">
-        <x:v>751</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="C73" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D73" s="10" t="s">
-        <x:v>748</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="E73" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F73" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G73" s="9" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="H73" s="10" t="n">
         <x:v>2</x:v>
@@ -13925,7 +14019,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="O73" s="9" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="P73" s="8" t="s">
         <x:v>169</x:v>
@@ -13936,25 +14030,25 @@
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="10" t="s">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="B74" s="8" t="s">
+        <x:v>751</x:v>
+      </x:c>
+      <x:c r="C74" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D74" s="10" t="s">
         <x:v>752</x:v>
-      </x:c>
-      <x:c r="B74" s="8" t="s">
-        <x:v>753</x:v>
-      </x:c>
-      <x:c r="C74" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D74" s="10" t="s">
-        <x:v>754</x:v>
       </x:c>
       <x:c r="E74" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F74" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G74" s="9" t="s">
-        <x:v>755</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="H74" s="10" t="n">
         <x:v>1</x:v>
@@ -13978,7 +14072,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="O74" s="9" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="P74" s="8" t="s">
         <x:v>169</x:v>
@@ -13989,25 +14083,25 @@
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="10" t="s">
-        <x:v>756</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B75" s="8" t="s">
-        <x:v>757</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="C75" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D75" s="10" t="s">
-        <x:v>754</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="E75" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F75" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G75" s="9" t="s">
-        <x:v>755</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="H75" s="10" t="n">
         <x:v>2</x:v>
@@ -14031,7 +14125,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="O75" s="9" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="P75" s="8" t="s">
         <x:v>169</x:v>
@@ -14042,25 +14136,25 @@
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="10" t="s">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="B76" s="8" t="s">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="C76" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D76" s="10" t="s">
         <x:v>758</x:v>
-      </x:c>
-      <x:c r="B76" s="8" t="s">
-        <x:v>759</x:v>
-      </x:c>
-      <x:c r="C76" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D76" s="10" t="s">
-        <x:v>760</x:v>
       </x:c>
       <x:c r="E76" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F76" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G76" s="9" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="H76" s="10" t="n">
         <x:v>1</x:v>
@@ -14081,10 +14175,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="N76" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O76" s="9" t="s">
-        <x:v>762</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="P76" s="8" t="s">
         <x:v>217</x:v>
@@ -14095,25 +14189,25 @@
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="10" t="s">
-        <x:v>763</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="B77" s="8" t="s">
-        <x:v>764</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="C77" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D77" s="10" t="s">
-        <x:v>760</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="E77" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F77" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G77" s="9" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="H77" s="10" t="n">
         <x:v>2</x:v>
@@ -14134,10 +14228,10 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="N77" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O77" s="9" t="s">
-        <x:v>762</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="P77" s="8" t="s">
         <x:v>217</x:v>
@@ -14148,25 +14242,25 @@
     </x:row>
     <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="10" t="s">
-        <x:v>765</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B78" s="8" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C78" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D78" s="10" t="s">
-        <x:v>760</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="E78" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F78" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G78" s="9" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="H78" s="10" t="n">
         <x:v>3</x:v>
@@ -14187,10 +14281,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="N78" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O78" s="9" t="s">
-        <x:v>762</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="P78" s="8" t="s">
         <x:v>217</x:v>
@@ -14201,25 +14295,25 @@
     </x:row>
     <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="10" t="s">
+        <x:v>765</x:v>
+      </x:c>
+      <x:c r="B79" s="8" t="s">
+        <x:v>766</x:v>
+      </x:c>
+      <x:c r="C79" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D79" s="10" t="s">
         <x:v>767</x:v>
-      </x:c>
-      <x:c r="B79" s="8" t="s">
-        <x:v>768</x:v>
-      </x:c>
-      <x:c r="C79" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D79" s="10" t="s">
-        <x:v>769</x:v>
       </x:c>
       <x:c r="E79" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F79" s="8" t="s">
-        <x:v>693</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G79" s="9" t="s">
-        <x:v>770</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="H79" s="10" t="n">
         <x:v>1</x:v>
@@ -14234,16 +14328,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L79" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M79" s="8" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="N79" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O79" s="9" t="s">
-        <x:v>771</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="P79" s="8" t="s">
         <x:v>169</x:v>
@@ -14254,25 +14348,25 @@
     </x:row>
     <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="10" t="s">
-        <x:v>772</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B80" s="8" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="C80" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D80" s="10" t="s">
-        <x:v>769</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="E80" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F80" s="8" t="s">
-        <x:v>693</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G80" s="9" t="s">
-        <x:v>770</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="H80" s="10" t="n">
         <x:v>2</x:v>
@@ -14287,16 +14381,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L80" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M80" s="8" t="n">
         <x:v>55</x:v>
       </x:c>
       <x:c r="N80" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O80" s="9" t="s">
-        <x:v>771</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="P80" s="8" t="s">
         <x:v>169</x:v>
@@ -14307,25 +14401,25 @@
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="10" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B81" s="8" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="C81" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D81" s="10" t="s">
-        <x:v>769</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="E81" s="8" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="F81" s="8" t="s">
-        <x:v>693</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G81" s="9" t="s">
-        <x:v>770</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="H81" s="10" t="n">
         <x:v>3</x:v>
@@ -14340,16 +14434,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L81" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M81" s="8" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="N81" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O81" s="9" t="s">
-        <x:v>771</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="P81" s="8" t="s">
         <x:v>169</x:v>
@@ -14360,25 +14454,25 @@
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="10" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="B82" s="8" t="s">
+        <x:v>775</x:v>
+      </x:c>
+      <x:c r="C82" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D82" s="10" t="s">
         <x:v>776</x:v>
       </x:c>
-      <x:c r="B82" s="8" t="s">
+      <x:c r="E82" s="8" t="s">
         <x:v>777</x:v>
       </x:c>
-      <x:c r="C82" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D82" s="10" t="s">
+      <x:c r="F82" s="8" t="s">
         <x:v>778</x:v>
       </x:c>
-      <x:c r="E82" s="8" t="s">
+      <x:c r="G82" s="9" t="s">
         <x:v>779</x:v>
-      </x:c>
-      <x:c r="F82" s="8" t="s">
-        <x:v>780</x:v>
-      </x:c>
-      <x:c r="G82" s="9" t="s">
-        <x:v>781</x:v>
       </x:c>
       <x:c r="H82" s="10" t="n">
         <x:v>1</x:v>
@@ -14393,16 +14487,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L82" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M82" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N82" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O82" s="9" t="s">
-        <x:v>782</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="P82" s="8" t="s">
         <x:v>217</x:v>
@@ -14413,25 +14507,25 @@
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="10" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="B83" s="8" t="s">
-        <x:v>784</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="C83" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D83" s="10" t="s">
+        <x:v>776</x:v>
+      </x:c>
+      <x:c r="E83" s="8" t="s">
+        <x:v>777</x:v>
+      </x:c>
+      <x:c r="F83" s="8" t="s">
         <x:v>778</x:v>
       </x:c>
-      <x:c r="E83" s="8" t="s">
+      <x:c r="G83" s="9" t="s">
         <x:v>779</x:v>
-      </x:c>
-      <x:c r="F83" s="8" t="s">
-        <x:v>780</x:v>
-      </x:c>
-      <x:c r="G83" s="9" t="s">
-        <x:v>781</x:v>
       </x:c>
       <x:c r="H83" s="10" t="n">
         <x:v>2</x:v>
@@ -14446,16 +14540,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="L83" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M83" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N83" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O83" s="9" t="s">
-        <x:v>782</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="P83" s="8" t="s">
         <x:v>217</x:v>
@@ -14466,25 +14560,25 @@
     </x:row>
     <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="10" t="s">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="B84" s="8" t="s">
+        <x:v>784</x:v>
+      </x:c>
+      <x:c r="C84" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D84" s="10" t="s">
         <x:v>785</x:v>
       </x:c>
-      <x:c r="B84" s="8" t="s">
+      <x:c r="E84" s="8" t="s">
+        <x:v>777</x:v>
+      </x:c>
+      <x:c r="F84" s="8" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="G84" s="9" t="s">
         <x:v>786</x:v>
-      </x:c>
-      <x:c r="C84" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D84" s="10" t="s">
-        <x:v>787</x:v>
-      </x:c>
-      <x:c r="E84" s="8" t="s">
-        <x:v>779</x:v>
-      </x:c>
-      <x:c r="F84" s="8" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="G84" s="9" t="s">
-        <x:v>788</x:v>
       </x:c>
       <x:c r="H84" s="10" t="n">
         <x:v>1</x:v>
@@ -14499,16 +14593,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L84" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M84" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="N84" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O84" s="9" t="s">
-        <x:v>789</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="P84" s="8" t="s">
         <x:v>217</x:v>
@@ -14519,25 +14613,25 @@
     </x:row>
     <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="10" t="s">
-        <x:v>790</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B85" s="8" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="C85" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D85" s="10" t="s">
-        <x:v>787</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="E85" s="8" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="F85" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G85" s="9" t="s">
-        <x:v>788</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="H85" s="10" t="n">
         <x:v>2</x:v>
@@ -14552,16 +14646,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="L85" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M85" s="8" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="N85" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O85" s="9" t="s">
-        <x:v>789</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="P85" s="8" t="s">
         <x:v>217</x:v>
@@ -14572,25 +14666,25 @@
     </x:row>
     <x:row r="86" ht="15" hidden="0" customHeight="1">
       <x:c r="A86" s="10" t="s">
+        <x:v>790</x:v>
+      </x:c>
+      <x:c r="B86" s="8" t="s">
+        <x:v>791</x:v>
+      </x:c>
+      <x:c r="C86" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D86" s="10" t="s">
         <x:v>792</x:v>
       </x:c>
-      <x:c r="B86" s="8" t="s">
+      <x:c r="E86" s="8" t="s">
+        <x:v>777</x:v>
+      </x:c>
+      <x:c r="F86" s="8" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="G86" s="9" t="s">
         <x:v>793</x:v>
-      </x:c>
-      <x:c r="C86" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D86" s="10" t="s">
-        <x:v>794</x:v>
-      </x:c>
-      <x:c r="E86" s="8" t="s">
-        <x:v>779</x:v>
-      </x:c>
-      <x:c r="F86" s="8" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="G86" s="9" t="s">
-        <x:v>795</x:v>
       </x:c>
       <x:c r="H86" s="10" t="n">
         <x:v>1</x:v>
@@ -14605,16 +14699,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L86" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M86" s="8" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="N86" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O86" s="9" t="s">
-        <x:v>796</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="P86" s="8" t="s">
         <x:v>169</x:v>
@@ -14625,25 +14719,25 @@
     </x:row>
     <x:row r="87" ht="15" hidden="0" customHeight="1">
       <x:c r="A87" s="10" t="s">
-        <x:v>797</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B87" s="8" t="s">
-        <x:v>798</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="C87" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D87" s="10" t="s">
-        <x:v>794</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="E87" s="8" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="F87" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G87" s="9" t="s">
-        <x:v>795</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="H87" s="10" t="n">
         <x:v>2</x:v>
@@ -14658,16 +14752,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L87" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M87" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="N87" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O87" s="9" t="s">
-        <x:v>796</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="P87" s="8" t="s">
         <x:v>169</x:v>
@@ -14678,25 +14772,25 @@
     </x:row>
     <x:row r="88" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A88" s="10" t="s">
+        <x:v>797</x:v>
+      </x:c>
+      <x:c r="B88" s="8" t="s">
+        <x:v>798</x:v>
+      </x:c>
+      <x:c r="C88" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D88" s="10" t="s">
         <x:v>799</x:v>
       </x:c>
-      <x:c r="B88" s="8" t="s">
+      <x:c r="E88" s="8" t="s">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="C88" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D88" s="10" t="s">
+      <x:c r="F88" s="8" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="G88" s="9" t="s">
         <x:v>801</x:v>
-      </x:c>
-      <x:c r="E88" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F88" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G88" s="9" t="s">
-        <x:v>803</x:v>
       </x:c>
       <x:c r="H88" s="10" t="n">
         <x:v>1</x:v>
@@ -14711,16 +14805,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L88" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M88" s="8" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="N88" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O88" s="9" t="s">
-        <x:v>804</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="P88" s="8" t="s">
         <x:v>169</x:v>
@@ -14731,25 +14825,25 @@
     </x:row>
     <x:row r="89" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A89" s="10" t="s">
-        <x:v>805</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B89" s="8" t="s">
-        <x:v>806</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="C89" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D89" s="10" t="s">
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="E89" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F89" s="8" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="G89" s="9" t="s">
         <x:v>801</x:v>
-      </x:c>
-      <x:c r="E89" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F89" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G89" s="9" t="s">
-        <x:v>803</x:v>
       </x:c>
       <x:c r="H89" s="10" t="n">
         <x:v>2</x:v>
@@ -14764,16 +14858,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="L89" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M89" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="N89" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O89" s="9" t="s">
-        <x:v>804</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="P89" s="8" t="s">
         <x:v>169</x:v>
@@ -14784,25 +14878,25 @@
     </x:row>
     <x:row r="90" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A90" s="10" t="s">
-        <x:v>807</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B90" s="8" t="s">
-        <x:v>808</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="C90" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D90" s="10" t="s">
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="E90" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F90" s="8" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="G90" s="9" t="s">
         <x:v>801</x:v>
-      </x:c>
-      <x:c r="E90" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F90" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G90" s="9" t="s">
-        <x:v>803</x:v>
       </x:c>
       <x:c r="H90" s="10" t="n">
         <x:v>3</x:v>
@@ -14817,16 +14911,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L90" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M90" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="N90" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O90" s="9" t="s">
-        <x:v>804</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="P90" s="8" t="s">
         <x:v>169</x:v>
@@ -14837,25 +14931,25 @@
     </x:row>
     <x:row r="91" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A91" s="10" t="s">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c r="B91" s="8" t="s">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="C91" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D91" s="10" t="s">
         <x:v>809</x:v>
       </x:c>
-      <x:c r="B91" s="8" t="s">
+      <x:c r="E91" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F91" s="8" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="G91" s="9" t="s">
         <x:v>810</x:v>
-      </x:c>
-      <x:c r="C91" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D91" s="10" t="s">
-        <x:v>811</x:v>
-      </x:c>
-      <x:c r="E91" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F91" s="8" t="s">
-        <x:v>693</x:v>
-      </x:c>
-      <x:c r="G91" s="9" t="s">
-        <x:v>812</x:v>
       </x:c>
       <x:c r="H91" s="10" t="n">
         <x:v>1</x:v>
@@ -14870,16 +14964,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L91" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M91" s="8" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="N91" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O91" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P91" s="8" t="s">
         <x:v>217</x:v>
@@ -14890,25 +14984,25 @@
     </x:row>
     <x:row r="92" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A92" s="10" t="s">
-        <x:v>814</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B92" s="8" t="s">
-        <x:v>751</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="C92" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D92" s="10" t="s">
-        <x:v>811</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="E92" s="8" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="F92" s="8" t="s">
-        <x:v>693</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G92" s="9" t="s">
-        <x:v>812</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="H92" s="10" t="n">
         <x:v>2</x:v>
@@ -14923,16 +15017,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="L92" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M92" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="N92" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O92" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P92" s="8" t="s">
         <x:v>217</x:v>
@@ -14943,25 +15037,25 @@
     </x:row>
     <x:row r="93" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A93" s="10" t="s">
-        <x:v>815</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B93" s="8" t="s">
-        <x:v>816</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="C93" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D93" s="10" t="s">
-        <x:v>811</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="E93" s="8" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="F93" s="8" t="s">
-        <x:v>693</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G93" s="9" t="s">
-        <x:v>812</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="H93" s="10" t="n">
         <x:v>3</x:v>
@@ -14976,16 +15070,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L93" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M93" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="N93" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O93" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P93" s="8" t="s">
         <x:v>217</x:v>
@@ -14996,25 +15090,25 @@
     </x:row>
     <x:row r="94" ht="15" hidden="0" customHeight="1">
       <x:c r="A94" s="10" t="s">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="B94" s="8" t="s">
+        <x:v>816</x:v>
+      </x:c>
+      <x:c r="C94" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D94" s="10" t="s">
         <x:v>817</x:v>
       </x:c>
-      <x:c r="B94" s="8" t="s">
+      <x:c r="E94" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F94" s="8" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="G94" s="9" t="s">
         <x:v>818</x:v>
-      </x:c>
-      <x:c r="C94" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D94" s="10" t="s">
-        <x:v>819</x:v>
-      </x:c>
-      <x:c r="E94" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F94" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G94" s="9" t="s">
-        <x:v>820</x:v>
       </x:c>
       <x:c r="H94" s="10" t="n">
         <x:v>1</x:v>
@@ -15029,16 +15123,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L94" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M94" s="8" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="N94" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O94" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P94" s="8" t="s">
         <x:v>169</x:v>
@@ -15049,25 +15143,25 @@
     </x:row>
     <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="10" t="s">
-        <x:v>821</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="B95" s="8" t="s">
-        <x:v>822</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="C95" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D95" s="10" t="s">
-        <x:v>819</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="E95" s="8" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="F95" s="8" t="s">
-        <x:v>541</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="G95" s="9" t="s">
-        <x:v>820</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="H95" s="10" t="n">
         <x:v>2</x:v>
@@ -15082,16 +15176,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L95" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M95" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="N95" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O95" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P95" s="8" t="s">
         <x:v>169</x:v>
@@ -15102,25 +15196,25 @@
     </x:row>
     <x:row r="96" ht="15" hidden="0" customHeight="1">
       <x:c r="A96" s="10" t="s">
+        <x:v>821</x:v>
+      </x:c>
+      <x:c r="B96" s="8" t="s">
+        <x:v>822</x:v>
+      </x:c>
+      <x:c r="C96" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D96" s="10" t="s">
         <x:v>823</x:v>
       </x:c>
-      <x:c r="B96" s="8" t="s">
+      <x:c r="E96" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F96" s="8" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="G96" s="9" t="s">
         <x:v>824</x:v>
-      </x:c>
-      <x:c r="C96" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D96" s="10" t="s">
-        <x:v>825</x:v>
-      </x:c>
-      <x:c r="E96" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F96" s="8" t="s">
-        <x:v>693</x:v>
-      </x:c>
-      <x:c r="G96" s="9" t="s">
-        <x:v>826</x:v>
       </x:c>
       <x:c r="H96" s="10" t="n">
         <x:v>1</x:v>
@@ -15135,16 +15229,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L96" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M96" s="8" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="N96" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O96" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P96" s="8" t="s">
         <x:v>217</x:v>
@@ -15155,25 +15249,25 @@
     </x:row>
     <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="10" t="s">
-        <x:v>827</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="B97" s="8" t="s">
-        <x:v>828</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="C97" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D97" s="10" t="s">
-        <x:v>825</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="E97" s="8" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="F97" s="8" t="s">
-        <x:v>693</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G97" s="9" t="s">
-        <x:v>826</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="H97" s="10" t="n">
         <x:v>2</x:v>
@@ -15188,16 +15282,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="L97" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M97" s="8" t="n">
         <x:v>35</x:v>
       </x:c>
       <x:c r="N97" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O97" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P97" s="8" t="s">
         <x:v>217</x:v>
@@ -15208,25 +15302,25 @@
     </x:row>
     <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="10" t="s">
+        <x:v>827</x:v>
+      </x:c>
+      <x:c r="B98" s="8" t="s">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="C98" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D98" s="10" t="s">
         <x:v>829</x:v>
       </x:c>
-      <x:c r="B98" s="8" t="s">
+      <x:c r="E98" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F98" s="8" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="G98" s="9" t="s">
         <x:v>830</x:v>
-      </x:c>
-      <x:c r="C98" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D98" s="10" t="s">
-        <x:v>831</x:v>
-      </x:c>
-      <x:c r="E98" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F98" s="8" t="s">
-        <x:v>693</x:v>
-      </x:c>
-      <x:c r="G98" s="9" t="s">
-        <x:v>832</x:v>
       </x:c>
       <x:c r="H98" s="10" t="n">
         <x:v>1</x:v>
@@ -15241,16 +15335,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L98" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M98" s="8" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="N98" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O98" s="9" t="s">
-        <x:v>833</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="P98" s="8" t="s">
         <x:v>217</x:v>
@@ -15261,25 +15355,25 @@
     </x:row>
     <x:row r="99" ht="15" hidden="0" customHeight="1">
       <x:c r="A99" s="10" t="s">
-        <x:v>834</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="B99" s="8" t="s">
-        <x:v>835</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="C99" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D99" s="10" t="s">
-        <x:v>831</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="E99" s="8" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="F99" s="8" t="s">
-        <x:v>693</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G99" s="9" t="s">
-        <x:v>832</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="H99" s="10" t="n">
         <x:v>2</x:v>
@@ -15294,16 +15388,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L99" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M99" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="N99" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O99" s="9" t="s">
-        <x:v>833</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="P99" s="8" t="s">
         <x:v>217</x:v>
@@ -15314,25 +15408,25 @@
     </x:row>
     <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="10" t="s">
+        <x:v>834</x:v>
+      </x:c>
+      <x:c r="B100" s="8" t="s">
+        <x:v>835</x:v>
+      </x:c>
+      <x:c r="C100" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D100" s="10" t="s">
         <x:v>836</x:v>
       </x:c>
-      <x:c r="B100" s="8" t="s">
+      <x:c r="E100" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F100" s="8" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="G100" s="9" t="s">
         <x:v>837</x:v>
-      </x:c>
-      <x:c r="C100" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D100" s="10" t="s">
-        <x:v>838</x:v>
-      </x:c>
-      <x:c r="E100" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F100" s="8" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="G100" s="9" t="s">
-        <x:v>839</x:v>
       </x:c>
       <x:c r="H100" s="10" t="n">
         <x:v>1</x:v>
@@ -15347,16 +15441,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L100" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M100" s="8" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="N100" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O100" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P100" s="8" t="s">
         <x:v>169</x:v>
@@ -15367,25 +15461,25 @@
     </x:row>
     <x:row r="101" ht="15" hidden="0" customHeight="1">
       <x:c r="A101" s="10" t="s">
-        <x:v>840</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="B101" s="8" t="s">
-        <x:v>841</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="C101" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D101" s="10" t="s">
-        <x:v>838</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="E101" s="8" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="F101" s="8" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="G101" s="9" t="s">
-        <x:v>839</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="H101" s="10" t="n">
         <x:v>2</x:v>
@@ -15400,16 +15494,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L101" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M101" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="N101" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O101" s="9" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="P101" s="8" t="s">
         <x:v>169</x:v>
@@ -15420,25 +15514,25 @@
     </x:row>
     <x:row r="102" ht="15" hidden="0" customHeight="1">
       <x:c r="A102" s="10" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="B102" s="8" t="s">
+        <x:v>841</x:v>
+      </x:c>
+      <x:c r="C102" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D102" s="10" t="s">
         <x:v>842</x:v>
       </x:c>
-      <x:c r="B102" s="8" t="s">
+      <x:c r="E102" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F102" s="8" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="G102" s="9" t="s">
         <x:v>843</x:v>
-      </x:c>
-      <x:c r="C102" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D102" s="10" t="s">
-        <x:v>844</x:v>
-      </x:c>
-      <x:c r="E102" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F102" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="G102" s="9" t="s">
-        <x:v>845</x:v>
       </x:c>
       <x:c r="H102" s="10" t="n">
         <x:v>1</x:v>
@@ -15453,16 +15547,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L102" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M102" s="8" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="N102" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O102" s="9" t="s">
-        <x:v>846</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="P102" s="8" t="s">
         <x:v>217</x:v>
@@ -15473,25 +15567,25 @@
     </x:row>
     <x:row r="103" ht="15" hidden="0" customHeight="1">
       <x:c r="A103" s="10" t="s">
-        <x:v>847</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="B103" s="8" t="s">
-        <x:v>848</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="C103" s="10" t="s">
-        <x:v>681</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D103" s="10" t="s">
-        <x:v>844</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="E103" s="8" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="F103" s="8" t="s">
-        <x:v>541</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="G103" s="9" t="s">
-        <x:v>845</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="H103" s="10" t="n">
         <x:v>2</x:v>
@@ -15506,16 +15600,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="L103" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M103" s="8" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="N103" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O103" s="9" t="s">
-        <x:v>846</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="P103" s="8" t="s">
         <x:v>217</x:v>
@@ -15526,25 +15620,25 @@
     </x:row>
     <x:row r="104" ht="15" hidden="0" customHeight="1">
       <x:c r="A104" s="10" t="s">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="B104" s="8" t="s">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c r="C104" s="10" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="D104" s="10" t="s">
         <x:v>849</x:v>
       </x:c>
-      <x:c r="B104" s="8" t="s">
+      <x:c r="E104" s="8" t="s">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="F104" s="8" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="G104" s="9" t="s">
         <x:v>850</x:v>
-      </x:c>
-      <x:c r="C104" s="10" t="s">
-        <x:v>681</x:v>
-      </x:c>
-      <x:c r="D104" s="10" t="s">
-        <x:v>851</x:v>
-      </x:c>
-      <x:c r="E104" s="8" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="F104" s="8" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="G104" s="9" t="s">
-        <x:v>852</x:v>
       </x:c>
       <x:c r="H104" s="10" t="n">
         <x:v>1</x:v>
@@ -15559,16 +15653,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L104" s="8" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="M104" s="8" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="N104" s="8" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O104" s="9" t="s">
-        <x:v>853</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="P104" s="8" t="s">
         <x:v>217</x:v>
@@ -15580,12 +15674,12 @@
     <x:row r="105" ht="15" hidden="0"/>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
       <x:c r="A106" s="4" t="s">
-        <x:v>854</x:v>
+        <x:v>852</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="10" t="s">
-        <x:v>566</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B107" s="10" t="n">
         <x:f aca="0">COUNTIF($F$5:$F$104,"*Collar*")</x:f>
@@ -15594,7 +15688,7 @@
     </x:row>
     <x:row r="108" ht="15" hidden="0" customHeight="1">
       <x:c r="A108" s="10" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="B108" s="10" t="n">
         <x:f aca="0">COUNTIF($F$5:$F$104,"*Harness*")</x:f>
@@ -15603,7 +15697,7 @@
     </x:row>
     <x:row r="109" ht="15" hidden="0" customHeight="1">
       <x:c r="A109" s="10" t="s">
-        <x:v>703</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="B109" s="10" t="n">
         <x:f aca="0">COUNTIF($F$5:$F$104,"*Charm*")</x:f>
@@ -15618,7 +15712,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R718d4b73d69b4e12"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0045ca2770ea40e1"/>
 </x:worksheet>
 </file>
 
@@ -15638,38 +15732,38 @@
   <x:sheetData>
     <x:row r="1" ht="17.25" hidden="0" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>855</x:v>
+        <x:v>853</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>856</x:v>
+        <x:v>854</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="31.5" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
         <x:v>142</x:v>
       </x:c>
       <x:c r="C4" s="7" t="s">
-        <x:v>857</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="D4" s="7" t="s">
         <x:v>148</x:v>
       </x:c>
       <x:c r="E4" s="7" t="s">
-        <x:v>858</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="F4" s="7" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="G4" s="7" t="s">
-        <x:v>859</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="H4" s="7" t="s">
-        <x:v>860</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="I4" s="7" t="s">
         <x:v>158</x:v>
@@ -15677,10 +15771,10 @@
     </x:row>
     <x:row r="5" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A5" s="10" t="s">
-        <x:v>861</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="B5" s="9" t="s">
-        <x:v>862</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="C5" s="8" t="n">
         <x:v>20</x:v>
@@ -15693,16 +15787,16 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="F5" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="G5" s="9" t="s">
+        <x:v>861</x:v>
+      </x:c>
+      <x:c r="H5" s="9" t="s">
+        <x:v>862</x:v>
+      </x:c>
+      <x:c r="I5" s="9" t="s">
         <x:v>863</x:v>
-      </x:c>
-      <x:c r="H5" s="9" t="s">
-        <x:v>864</x:v>
-      </x:c>
-      <x:c r="I5" s="9" t="s">
-        <x:v>865</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -15710,7 +15804,7 @@
         <x:v>304</x:v>
       </x:c>
       <x:c r="B6" s="9" t="s">
-        <x:v>866</x:v>
+        <x:v>864</x:v>
       </x:c>
       <x:c r="C6" s="8" t="n">
         <x:v>15</x:v>
@@ -15723,24 +15817,24 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="F6" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="G6" s="9" t="s">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="H6" s="9" t="s">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="I6" s="9" t="s">
         <x:v>867</x:v>
-      </x:c>
-      <x:c r="H6" s="9" t="s">
-        <x:v>868</x:v>
-      </x:c>
-      <x:c r="I6" s="9" t="s">
-        <x:v>869</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="10" t="s">
-        <x:v>870</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="B7" s="9" t="s">
-        <x:v>871</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="C7" s="8" t="n">
         <x:v>18</x:v>
@@ -15753,24 +15847,24 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="F7" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="G7" s="9" t="s">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c r="H7" s="9" t="s">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="I7" s="9" t="s">
         <x:v>872</x:v>
-      </x:c>
-      <x:c r="H7" s="9" t="s">
-        <x:v>873</x:v>
-      </x:c>
-      <x:c r="I7" s="9" t="s">
-        <x:v>874</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="10" t="s">
-        <x:v>875</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="B8" s="9" t="s">
-        <x:v>876</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="C8" s="8" t="n">
         <x:v>25</x:v>
@@ -15783,24 +15877,24 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="F8" s="8" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="G8" s="9" t="s">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="H8" s="9" t="s">
+        <x:v>876</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
         <x:v>877</x:v>
-      </x:c>
-      <x:c r="H8" s="9" t="s">
-        <x:v>878</x:v>
-      </x:c>
-      <x:c r="I8" s="9" t="s">
-        <x:v>879</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="10" t="s">
-        <x:v>880</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="B9" s="9" t="s">
-        <x:v>881</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="C9" s="8" t="n">
         <x:v>2</x:v>
@@ -15816,13 +15910,13 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="G9" s="9" t="s">
+        <x:v>880</x:v>
+      </x:c>
+      <x:c r="H9" s="9" t="s">
+        <x:v>881</x:v>
+      </x:c>
+      <x:c r="I9" s="9" t="s">
         <x:v>882</x:v>
-      </x:c>
-      <x:c r="H9" s="9" t="s">
-        <x:v>883</x:v>
-      </x:c>
-      <x:c r="I9" s="9" t="s">
-        <x:v>884</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -15830,7 +15924,7 @@
         <x:v>371</x:v>
       </x:c>
       <x:c r="B10" s="9" t="s">
-        <x:v>885</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="C10" s="8" t="n">
         <x:v>3</x:v>
@@ -15846,21 +15940,21 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="G10" s="9" t="s">
+        <x:v>884</x:v>
+      </x:c>
+      <x:c r="H10" s="9" t="s">
+        <x:v>885</x:v>
+      </x:c>
+      <x:c r="I10" s="9" t="s">
         <x:v>886</x:v>
-      </x:c>
-      <x:c r="H10" s="9" t="s">
-        <x:v>887</x:v>
-      </x:c>
-      <x:c r="I10" s="9" t="s">
-        <x:v>888</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="23.25" hidden="0" customHeight="1">
       <x:c r="A11" s="10" t="s">
-        <x:v>889</x:v>
+        <x:v>887</x:v>
       </x:c>
       <x:c r="B11" s="9" t="s">
-        <x:v>890</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="C11" s="8" t="n">
         <x:v>20</x:v>
@@ -15873,16 +15967,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="F11" s="8" t="s">
+        <x:v>889</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="s">
+        <x:v>875</x:v>
+      </x:c>
+      <x:c r="H11" s="9" t="s">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="I11" s="9" t="s">
         <x:v>891</x:v>
-      </x:c>
-      <x:c r="G11" s="9" t="s">
-        <x:v>877</x:v>
-      </x:c>
-      <x:c r="H11" s="9" t="s">
-        <x:v>892</x:v>
-      </x:c>
-      <x:c r="I11" s="9" t="s">
-        <x:v>893</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/pet-expansion/pet-design.xlsx
+++ b/docs/pet-expansion/pet-design.xlsx
@@ -3854,7 +3854,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="8" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C9" s="10" t="s">
         <x:v>42</x:v>
